--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FA6628-7CA2-4688-88E6-2E46E7DF649E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6A0019-7378-4C4C-900C-DADC3BD5AD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="453">
   <si>
     <t>matricula</t>
   </si>
@@ -1367,6 +1367,18 @@
   </si>
   <si>
     <t>eabc83fb-f110-472e-b134-94ba69f47022</t>
+  </si>
+  <si>
+    <t>0ac5c6a4-d866-4e26-8943-1242489e2a97</t>
+  </si>
+  <si>
+    <t>ALESSANDRA SANTOS SANTANA</t>
+  </si>
+  <si>
+    <t>VANESSA CRISTINA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>74d5c30f-4192-4ccd-8208-3ce07dbc2168</t>
   </si>
 </sst>
 </file>
@@ -1750,7 +1762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C227"/>
+  <dimension ref="A1:C229"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="42.61328125" bestFit="1" customWidth="1"/>
@@ -4254,6 +4266,28 @@
         <v>448</v>
       </c>
     </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A228" s="4">
+        <v>5374</v>
+      </c>
+      <c r="B228" t="s">
+        <v>450</v>
+      </c>
+      <c r="C228" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A229" s="4">
+        <v>5377</v>
+      </c>
+      <c r="B229" t="s">
+        <v>451</v>
+      </c>
+      <c r="C229" t="s">
+        <v>452</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b564e36bc34a5810/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6A0019-7378-4C4C-900C-DADC3BD5AD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3448C58B-31D6-4BE7-B4C0-530C24BDC490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="469">
   <si>
     <t>matricula</t>
   </si>
@@ -1379,13 +1379,61 @@
   </si>
   <si>
     <t>74d5c30f-4192-4ccd-8208-3ce07dbc2168</t>
+  </si>
+  <si>
+    <t>CLECIA JESUS DIAS</t>
+  </si>
+  <si>
+    <t>13f5dd41-75df-47fb-90d0-ec07996a54fd</t>
+  </si>
+  <si>
+    <t>CLEIDE RODRIGUES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>01bbe8dd-0de7-408c-94f4-65d2188bfdea</t>
+  </si>
+  <si>
+    <t>CRISTIANE SANTANA BARBOZA</t>
+  </si>
+  <si>
+    <t>2660b31a-ebe3-4d7a-a54a-9ab4016f4a80</t>
+  </si>
+  <si>
+    <t>DANIELA BARBOSA DA SILVA</t>
+  </si>
+  <si>
+    <t>75c170e3-fc91-4e29-a805-f09c456e00e5</t>
+  </si>
+  <si>
+    <t>GABRIELLY APARECIDA CANDIDO DA SILVA</t>
+  </si>
+  <si>
+    <t>c2522e5f-8b2b-4e2d-8ae2-3f31e8b8f612</t>
+  </si>
+  <si>
+    <t>LENITA SANTANA NASCIMENTO</t>
+  </si>
+  <si>
+    <t>24482151-ff1a-4d3c-a533-b0ab6823f052</t>
+  </si>
+  <si>
+    <t>MARIA DE FATIMA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>ROSILENI DE FATIMA FERNANDES</t>
+  </si>
+  <si>
+    <t>c793879a-b57d-4685-81cf-7b9a0589138b</t>
+  </si>
+  <si>
+    <t>11a6d214-fbf4-41c3-ab4a-ec4555a20fad</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1400,6 +1448,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5A5C5E"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1443,7 +1497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1458,11 +1512,75 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1762,7 +1880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C229"/>
+  <dimension ref="A1:C237"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="42.61328125" bestFit="1" customWidth="1"/>
@@ -4213,7 +4331,7 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A223" s="4">
-        <v>5367</v>
+        <v>5369</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>439</v>
@@ -4288,7 +4406,102 @@
         <v>452</v>
       </c>
     </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A230">
+        <v>5384</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="C230" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A231">
+        <v>5383</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="C231" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A232">
+        <v>5379</v>
+      </c>
+      <c r="B232" t="s">
+        <v>457</v>
+      </c>
+      <c r="C232" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A233">
+        <v>5387</v>
+      </c>
+      <c r="B233" t="s">
+        <v>459</v>
+      </c>
+      <c r="C233" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A234">
+        <v>5380</v>
+      </c>
+      <c r="B234" t="s">
+        <v>461</v>
+      </c>
+      <c r="C234" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A235">
+        <v>5381</v>
+      </c>
+      <c r="B235" t="s">
+        <v>463</v>
+      </c>
+      <c r="C235" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A236">
+        <v>5388</v>
+      </c>
+      <c r="B236" t="s">
+        <v>465</v>
+      </c>
+      <c r="C236" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A237">
+        <v>5367</v>
+      </c>
+      <c r="B237" t="s">
+        <v>466</v>
+      </c>
+      <c r="C237" t="s">
+        <v>467</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b564e36bc34a5810/Área de Trabalho/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3448C58B-31D6-4BE7-B4C0-530C24BDC490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E0C32D-D0B3-4B10-81A6-8BBD1269127E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="471">
   <si>
     <t>matricula</t>
   </si>
@@ -1427,6 +1427,12 @@
   </si>
   <si>
     <t>11a6d214-fbf4-41c3-ab4a-ec4555a20fad</t>
+  </si>
+  <si>
+    <t>ALCIONE MAGALHAES MESQUITA</t>
+  </si>
+  <si>
+    <t>66193f15-5e6c-436b-97c7-f0cb5b423d15</t>
   </si>
 </sst>
 </file>
@@ -1519,37 +1525,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1880,7 +1856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C237"/>
+  <dimension ref="A1:C238"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="42.61328125" bestFit="1" customWidth="1"/>
@@ -4494,10 +4470,21 @@
         <v>467</v>
       </c>
     </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A238">
+        <v>5369</v>
+      </c>
+      <c r="B238" t="s">
+        <v>469</v>
+      </c>
+      <c r="C238" t="s">
+        <v>470</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E0C32D-D0B3-4B10-81A6-8BBD1269127E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE77649-F5E7-4AB0-AC05-6BEC37CB8692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4472,7 +4472,7 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A238">
-        <v>5369</v>
+        <v>5389</v>
       </c>
       <c r="B238" t="s">
         <v>469</v>
